--- a/tools/importer/reports/import-homepage.report.xlsx
+++ b/tools/importer/reports/import-homepage.report.xlsx
@@ -40,7 +40,7 @@
     <t>index.report.json</t>
   </si>
   <si>
-    <t>["hero-saga","hero-saga","cards-campaign","cards-campaign","cards-tiles","cards-articles","columns-trust","form"]</t>
+    <t>["hero-saga","cards-features","cards-services","cards-services","cards-services","cards-services","cards-tiles"]</t>
   </si>
   <si>
     <t>index</t>
@@ -52,13 +52,13 @@
     <t>homepage</t>
   </si>
   <si>
-    <t>2026-04-16T10:16:17.165Z</t>
-  </si>
-  <si>
-    <t>Welcome to Saga – Over 50s insurance, holidays and money</t>
-  </si>
-  <si>
-    <t>https://www.saga.co.uk/</t>
+    <t>2026-06-12T09:51:16.890Z</t>
+  </si>
+  <si>
+    <t>How you feel tomorrow starts today | Nuffield Health</t>
+  </si>
+  <si>
+    <t>https://www.nuffieldhealth.com/</t>
   </si>
 </sst>
 </file>
@@ -456,7 +456,7 @@
     <col min="5" max="5" width="10" customWidth="1"/>
     <col min="6" max="6" width="26" customWidth="1"/>
     <col min="7" max="7" width="50" customWidth="1"/>
-    <col min="8" max="8" width="25" customWidth="1"/>
+    <col min="8" max="8" width="33" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.25">
